--- a/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
+++ b/docs/Voyager-UIUX-Timesheet-Aug2026.xlsx
@@ -90,7 +90,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -112,11 +112,55 @@
         <color rgb="00C3CBD6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C3CBD6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C3CBD6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C3CBD6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C3CBD6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C3CBD6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C3CBD6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C3CBD6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C3CBD6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +224,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -545,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -563,7 +609,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary by day — for invoicing (6 Aug – 6 Sep 2026)</t>
+          <t>Summary by day — for invoicing (6 Aug – 26 Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -596,7 +642,7 @@
         </is>
       </c>
       <c r="C5" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A5,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A5,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -612,7 +658,7 @@
         </is>
       </c>
       <c r="C6" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A6,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A6,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -628,7 +674,7 @@
         </is>
       </c>
       <c r="C7" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A7,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A7,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -644,7 +690,7 @@
         </is>
       </c>
       <c r="C8" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A8,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A8,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -660,7 +706,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A9,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A9,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -676,7 +722,7 @@
         </is>
       </c>
       <c r="C10" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A10,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A10,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +738,7 @@
         </is>
       </c>
       <c r="C11" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A11,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A11,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -708,7 +754,7 @@
         </is>
       </c>
       <c r="C12" s="22">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A12,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A12,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -724,7 +770,7 @@
         </is>
       </c>
       <c r="C13" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A13,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A13,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -740,7 +786,7 @@
         </is>
       </c>
       <c r="C14" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A14,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A14,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -756,7 +802,7 @@
         </is>
       </c>
       <c r="C15" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A15,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A15,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -772,7 +818,7 @@
         </is>
       </c>
       <c r="C16" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A16,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A16,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +834,7 @@
         </is>
       </c>
       <c r="C17" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A17,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A17,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -804,7 +850,7 @@
         </is>
       </c>
       <c r="C18" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A18,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A18,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +866,7 @@
         </is>
       </c>
       <c r="C19" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A19,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A19,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -836,7 +882,7 @@
         </is>
       </c>
       <c r="C20" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A20,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A20,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -852,7 +898,7 @@
         </is>
       </c>
       <c r="C21" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A21,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A21,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -868,7 +914,7 @@
         </is>
       </c>
       <c r="C22" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A22,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A22,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
@@ -884,32 +930,193 @@
         </is>
       </c>
       <c r="C23" s="19">
-        <f>SUMIF(Timesheet!$A$6:$A$70,A23,Timesheet!$C$6:$C$70)</f>
+        <f>SUMIF(Timesheet!$A$6:$A$103,A23,Timesheet!$C$6:$C$103)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Work log and timesheet updated; ten design-system questions answered and the colour palette set</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A24,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Colour roles rolled out, dark mode built and swept, two more KPI summaries</t>
+        </is>
+      </c>
+      <c r="C25" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A25,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Before-and-after screenshots, login redesign, states and a chart defect</t>
+        </is>
+      </c>
+      <c r="C28" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A28,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Render check, 44px touch targets app-wide, phone layout, keyboard focus check</t>
+        </is>
+      </c>
+      <c r="C29" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A29,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Checks moved into CI, README reconciled, three defects fixed</t>
+        </is>
+      </c>
+      <c r="C30" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A30,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Checks clean up after themselves, hover check, client document shortened, phone action row</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A31,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>The RFQ's related records point at other screens; Historical RFQ names a real RFQ</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A32,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Button placement checked against the published standards, and the client document updated</t>
+        </is>
+      </c>
+      <c r="C33" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A33,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Logo research and first directions</t>
+        </is>
+      </c>
+      <c r="C34" s="19">
+        <f>SUMIF(Timesheet!$A$6:$A$103,A34,Timesheet!$C$6:$C$103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C24" s="23">
-        <f>SUM(C5:C23)</f>
+      <c r="C35" s="23">
+        <f>SUM(C5:C34)</f>
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>This sheet totals the Timesheet tab with SUMIF, so the two cannot disagree. Editing an hour there updates it here.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Hours are estimated from scope. Reconcile against your own record before invoicing. The 28 Aug – 6 Sep entries correspond to work packages WP14–WP23 in docs/worklog.md; 26–27 Aug were already logged.</t>
         </is>
@@ -930,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -956,7 +1163,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Work log: 6 August – 6 September 2026</t>
+          <t>Work log: 6 August – 26 September 2026</t>
         </is>
       </c>
     </row>
@@ -2282,77 +2489,746 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="12" t="n"/>
-      <c r="B71" s="13" t="inlineStr">
+    <row r="71" ht="58" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Brought the work log and this timesheet up to date, including 19.5 hours that had not been counted.</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="58" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Answered ten design-system questions and set the Voyager IQ colour palette: one brand hue, with named roles under it.</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: design decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="58" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Moved 553 colour references onto those named roles, so changing a colour is one edit instead of a search.</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="58" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Built dark mode: the switch, the Kendo bridge and every screen checked. Four defects found and fixed.</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: dark mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="58" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Part Master and Bill of Materials gained the KPI summary and an empty state that tells the truth.</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="58" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Put Part Master's columns back into the live system's order.</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="58" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>The design system page now documents the system that actually exists.</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: design system</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="58" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Crawled all 45 screens for errors. Fixed a date frozen three weeks earlier and a placeholder that could not name itself.</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="58" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Grid fixes: the select-all checkbox, the selection bar, the part-number link, and a link that reads as a link without using colour.</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="58" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Re-checked the live system after it changed, and re-extracted its shipped code so the next check is repeatable.</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="58" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Built the Engineering group and its screens: Part Master detail, Bill of Materials, Manufacturers, MPN and Packing Lists.</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="58" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Added the two missing state changes, Confirm RFQ and Cancel RFQ, and a second way into a record.</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="58" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>The Bill of Materials list now lists bills of materials rather than parts.</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="58" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>One toolbar across all six list screens.</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="58" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Wrote the before-and-after document for the client, with an honest assessment of KendoReact.</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="58" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Captured real before-and-after screenshots of the two Quotations flows.</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="58" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Redesigned the login screen so the brand panel earns its half.</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="58" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Checked the six new screens and gave them back their loading and empty states. Fixed a chart with an invisible series.</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="58" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Wrote a check that catches the three defects a stylesheet cannot show you, and fixed what it found.</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="58" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Raised every touch target on a phone to 44px, across the whole application.</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Quality / accessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="58" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Phone layout: chrome above each list cut from 348px to 258px, and a type scale sized for a finger.</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="58" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Added a keyboard focus check and a dark-mode sweep, then fixed the phone defects the checks had been hiding.</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="58" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Put the checks into CI, so something other than memory runs them on every push.</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="58" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Reconciled the README and the deployment notes with the repository they describe.</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="58" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Three defects fixed: the KPI band, controls unreachable on a phone (pager, filters, column chooser), and hover on list links.</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="58" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Made the checks clean up after themselves, and added a hover check.</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="58" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Shortened the client document and refreshed its screenshots.</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="58" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Page actions now wrap on a phone instead of scrolling with the last button cut off.</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="58" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Reviewed the RFQ's related-records row: five of its six buttons only opened tabs on the same page. Replaced them with links to other screens, after researching Odoo, SAP and Salesforce.</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Research + build</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="58" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Historical RFQ now names a real earlier RFQ of the same customer.</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Defect fixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="58" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Checked the demo feedback on button placement against the published standards (Fiori, Material, Fluent, Microsoft, NN/g, GOV.UK). Moved the destructive action away from the primary, and kept Next at the bottom of a wizard step.</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Research + build</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="58" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Client document: the button-placement argument, four new questions and a refreshed screenshot.</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Deliverable: client document</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="58" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Logo research: how ERP and electronics-manufacturing brands mark themselves, and first directions for a Voyager IQ mark.</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Research: logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="n"/>
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C71" s="14">
-        <f>SUM(C6:C70)</f>
+      <c r="C104" s="14">
+        <f>SUM(C6:C103)</f>
         <v/>
       </c>
-      <c r="D71" s="12" t="n"/>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="15" t="inlineStr">
+      <c r="D104" s="12" t="n"/>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="15" t="inlineStr">
         <is>
           <t>Notes on this log</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
         <is>
           <t>•  Entries for 06/08 and 10/08 were supplied by the consultant; all other entries are reconstructed from the project's version-control history, which records 152 commits across 19 August – 6 September.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
         <is>
           <t>•  Hours are an estimate of the effort each task represents. Version control records when work was committed, not how long it took, so these figures should be reconciled against the consultant's own record before invoicing.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
         <is>
           <t>•  Three entries are marked as risk avoided rather than features delivered. The metadata verification (24/08) caught option lists that would have caused the built system to reject valid user input. The bundle forensics (24/08) recovered specifications for features that would otherwise have been rebuilt from guesswork. The requirements decisions (24/08) avoid a change-management cost across 51 screens and every current user. Two later entries carry the same mark: the export-control field (27/08), which was rendering as a label instead of restricting access, and the component sweep of 31/08, corrected after its own method proved unable to detect one of the components it reported on.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>•  The prototype now uses KendoReact. The line this replaces said the opposite, and was true when written: no licence existed. The key arrived on 31/08, and the client then chose Kendo so the mockup would not look unlike the system their staff already use. Three component families were deliberately not migrated, each for a stated reason.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>•  Current phase covers layout and user experience. Visual design — colour, spacing, typography and component styling — is a later phase, so that it is not done twice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>•  Layout and user experience are done. The colour system was set on 7 September; logo and visual identity started on 26 September.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
         <is>
           <t>•  Correction, 07/09: the 26/08 and 27/08 entries had been appended BELOW this notes block and were excluded from the total and from the Summary tab, understating the log by 19.5 hours. They are now in the table above, unchanged, and both totals cover every row.</t>
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="16" t="inlineStr">
+        <is>
+          <t>•  Update, 26/09: entries for 7–26 September added, reconstructed from version control (84 commits across 7–20 September). Colour and dark mode are done; logo work started 26/09.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A76:D76"/>
+  <mergeCells count="7">
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A108:D108"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
